--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +555,76 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>ID_20260602085124</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACACIAS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MUSACEUM C.A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>36866</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PCP DANIEL  GARCIA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RESPONSABLE NO COLOCO PESO DE TARA EN EL APLICATIVO</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>INC_155544_0.png INC_155544_1.png</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ID_20260602155545</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,6 +625,76 @@
       <c r="N3" t="inlineStr">
         <is>
           <t>ID_20260602155545</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACACIAS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MUSACEUM C.A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>36866</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PCP DANIEL GARCIA</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>RESPONSABLE INGRESO SKU A DESTIEMPO.</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>INC_160039_0.png</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ID_20260602160039</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>INC_160039_0.png</t>
+          <t>INC_160039_0.png INC_160113_0.png</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,6 +695,76 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>ID_20260602160039</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ACACIAS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LATIN FRUITS C.A</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>006886</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GERENTE LOURDES PALACIOS </t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>RESPONSABLE MONTO COPIA DE FACTURA Y LA MISMA SERA REEMPLAZADA</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>INC_170712_0.png</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>ID_20260602170712</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -765,6 +765,71 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>ID_20260602170712</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ACACIAS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>37031</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>LOURDES PALACIOS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ID_20260603100142</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -827,6 +827,11 @@
           <t>NINGUNA</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>INC_100221_0.png</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>ID_20260603100142</t>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,6 +842,76 @@
       <c r="N6" t="inlineStr">
         <is>
           <t>ID_20260603100142</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ACACIAS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>37031</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>LOURDES PALACIOS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>INC_101053_0.jpeg</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ID_20260603101053</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>INC_101053_0.jpeg</t>
+          <t>INC_101053_0.jpeg INC_101352_0.png</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -798,7 +798,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>DEVOLUCION</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -808,21 +808,21 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FISCALIZACIÓN A DESTIEMPO</t>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO D</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
+          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>7.62</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -831,17 +831,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>COBRO</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>INC_100221_0.png</t>
+          <t>INC_101053_0.jpeg INC_101352_0.png</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ID_20260603100142</t>
+          <t>ID_20260603101053</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DEVOLUCION</t>
+          <t>RECEPCION</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -878,21 +878,21 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TIPO D</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
-        </is>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>7.62</v>
+          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -901,17 +901,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>COBRO</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>INC_101053_0.jpeg INC_101352_0.png</t>
+          <t>INC_100221_0.png INC_101619_0.png</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ID_20260603101053</t>
+          <t>ID_20260603100142</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -821,7 +814,7 @@
           <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
         </is>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" t="n">
         <v>7.62</v>
       </c>
       <c r="K6" t="inlineStr">
@@ -906,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>INC_100221_0.png INC_101619_0.png</t>
+          <t>INC_101619_0.png</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>INC_101619_0.png</t>
+          <t>INC_101619_0.png INC_101719_1.png</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -814,7 +821,7 @@
           <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="1" t="n">
         <v>7.62</v>
       </c>
       <c r="K6" t="inlineStr">

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -821,7 +814,7 @@
           <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
         </is>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" t="n">
         <v>7.62</v>
       </c>
       <c r="K6" t="inlineStr">
@@ -836,7 +829,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>INC_101053_0.jpeg INC_101352_0.png</t>
+          <t>INC_101352_0.png</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DEVOLUCION</t>
+          <t>RECEPCION</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -801,21 +801,21 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TIPO D</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
+          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7.62</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>COBRO</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>INC_101352_0.png</t>
+          <t>INC_101619_0.png INC_101719_1.png</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ID_20260603101053</t>
+          <t>ID_20260603100142</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>DEVOLUCION</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -871,40 +871,40 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FISCALIZACIÓN A DESTIEMPO</t>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO D</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
+          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>7.62</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>COB_114708_0.png</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>COBRO</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>INC_101619_0.png INC_101719_1.png</t>
+          <t>INC_101352_0.png</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ID_20260603100142</t>
+          <t>ID_20260603101053</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -884,7 +891,7 @@
           <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="1" t="n">
         <v>7.62</v>
       </c>
       <c r="K7" t="inlineStr">

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -556,7 +549,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>INC_085124_0.jpeg INC_085124_1.jpeg</t>
+          <t>INC_085124_1.jpeg</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -891,7 +884,7 @@
           <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
         </is>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" t="n">
         <v>7.62</v>
       </c>
       <c r="K7" t="inlineStr">

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -547,11 +547,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>INC_085124_1.jpeg</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>ID_20260602085124</t>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>INC_155544_0.png INC_155544_1.png</t>
+          <t>INC_155544_1.png</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -613,11 +613,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>INC_155544_1.png</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>ID_20260602155545</t>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>INC_160039_0.png INC_160113_0.png</t>
+          <t>INC_160113_0.png</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -679,11 +679,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>INC_160113_0.png</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>ID_20260602160039</t>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -817,7 +817,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>INC_101619_0.png INC_101719_1.png</t>
+          <t>INC_101719_1.png</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -885,11 +885,7 @@
           <t>COBRO</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>INC_101352_0.png</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>ID_20260603101053</t>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -815,11 +815,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>INC_101719_1.png</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>ID_20260603100142</t>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -745,11 +745,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>INC_170712_0.png</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>ID_20260602170712</t>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -869,7 +869,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>COB_114708_0.png</t>
+          <t>SIN_FOTO</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -479,12 +486,12 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>FOTO_INCIDENCIA</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ID</t>
         </is>
       </c>
     </row>
@@ -547,8 +554,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>ID_20260602085124</t>
         </is>
@@ -613,8 +619,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>ID_20260602155545</t>
         </is>
@@ -679,8 +684,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>ID_20260602160039</t>
         </is>
@@ -745,8 +749,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>ID_20260602170712</t>
         </is>
@@ -811,8 +814,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>ID_20260603100142</t>
         </is>
@@ -864,12 +866,12 @@
           <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>7.62</v>
+      <c r="J7" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>COB_124837_0.jpeg</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -877,8 +879,7 @@
           <t>COBRO</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>ID_20260603101053</t>
         </is>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>DEVOLUCION</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -788,35 +788,35 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FISCALIZACIÓN A DESTIEMPO</t>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO D</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
-        </is>
-      </c>
-      <c r="J6" t="n">
+          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>COB_124837_0.jpeg</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>COBRO</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ID_20260603100142</t>
+          <t>ID_20260603101053</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DEVOLUCION</t>
+          <t>RECEPCION</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -853,35 +853,40 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TIPO D</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
-        </is>
-      </c>
-      <c r="J7" s="1" t="n">
+          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>COB_124837_0.jpeg</t>
+          <t>SIN_FOTO</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>COBRO</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ID_20260603101053</t>
+          <t>ID_20260603100142</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>INC_124933_0.png INC_124933_1.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -698,60 +698,60 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LATIN FRUITS C.A</t>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>006886</t>
+          <t>37031</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>DEVOLUCION</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GERENTE LOURDES PALACIOS </t>
+          <t>LOURDES PALACIOS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DOCUMENTACIÓN ERRÓNEA</t>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO D</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>RESPONSABLE MONTO COPIA DE FACTURA Y LA MISMA SERA REEMPLAZADA</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>COB_124837_0.jpeg</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>COBRO</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ID_20260602170712</t>
+          <t>ID_20260603101053</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DEVOLUCION</t>
+          <t>RECEPCION</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -788,35 +788,40 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TIPO D</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="n">
+          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>COB_124837_0.jpeg</t>
+          <t>SIN_FOTO</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>COBRO</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ID_20260603101053</t>
+          <t>ID_20260603100142</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>INC_124933_0.png INC_124933_1.png</t>
         </is>
       </c>
     </row>
@@ -828,17 +833,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+          <t>LATIN FRUITS C.A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>37031</t>
+          <t>006886</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -848,12 +853,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LOURDES PALACIOS</t>
+          <t xml:space="preserve">GERENTE LOURDES PALACIOS </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FISCALIZACIÓN A DESTIEMPO</t>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -863,7 +868,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
+          <t>RESPONSABLE MONTO COPIA DE FACTURA Y LA MISMA SERA REEMPLAZADA</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -881,12 +886,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ID_20260603100142</t>
+          <t>ID_20260602170712</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>INC_124933_0.png INC_124933_1.png</t>
+          <t>INC_125257_0.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -588,22 +588,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PCP DANIEL  GARCIA</t>
+          <t xml:space="preserve"> PCP DANIEL GARCIA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TIPO A</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RESPONSABLE NO COLOCO PESO DE TARA EN EL APLICATIVO</t>
+          <t>RESPONSABLE INGRESO SKU A DESTIEMPO.</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -621,7 +621,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ID_20260602155545</t>
+          <t>ID_20260602160039</t>
         </is>
       </c>
     </row>
@@ -633,17 +633,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MUSACEUM C.A</t>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>36866</t>
+          <t>37031</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -653,40 +653,40 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PCP DANIEL GARCIA</t>
+          <t>LOURDES PALACIOS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FISCALIZACIÓN A DESTIEMPO</t>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO D</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>RESPONSABLE INGRESO SKU A DESTIEMPO.</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>COB_124837_0.jpeg</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>COBRO</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ID_20260602160039</t>
+          <t>ID_20260603101053</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DEVOLUCION</t>
+          <t>RECEPCION</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -723,35 +723,40 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TIPO D</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
-        </is>
-      </c>
-      <c r="J5" s="1" t="n">
+          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>COB_124837_0.jpeg</t>
+          <t>SIN_FOTO</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>COBRO</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ID_20260603101053</t>
+          <t>ID_20260603100142</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>INC_124933_0.png INC_124933_1.png</t>
         </is>
       </c>
     </row>
@@ -763,17 +768,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+          <t>LATIN FRUITS C.A</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37031</t>
+          <t>006886</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +788,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LOURDES PALACIOS</t>
+          <t xml:space="preserve">GERENTE LOURDES PALACIOS </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FISCALIZACIÓN A DESTIEMPO</t>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,7 +803,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
+          <t>RESPONSABLE MONTO COPIA DE FACTURA Y LA MISMA SERA REEMPLAZADA</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -816,12 +821,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ID_20260603100142</t>
+          <t>ID_20260602170712</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>INC_124933_0.png INC_124933_1.png</t>
+          <t>INC_125257_0.png</t>
         </is>
       </c>
     </row>
@@ -833,12 +838,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LATIN FRUITS C.A</t>
+          <t>MUSACEUM C.A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>006886</t>
+          <t>36866</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -848,27 +853,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>DEVOLUCION</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GERENTE LOURDES PALACIOS </t>
+          <t>PCP DANIEL  GARCIA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DOCUMENTACIÓN ERRÓNEA</t>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO A</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>RESPONSABLE MONTO COPIA DE FACTURA Y LA MISMA SERA REEMPLAZADA</t>
+          <t>RESPONSABLE NO COLOCO PESO DE TARA EN EL APLICATIVO</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -886,12 +891,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ID_20260602170712</t>
+          <t>ID_20260602155545</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>INC_125257_0.png</t>
+          <t>INC_130212_0.png INC_130212_1.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,6 +552,7 @@
           <t>ID_20260602085124</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -568,17 +562,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MUSACEUM C.A</t>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36866</t>
+          <t>37031</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,22 +582,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PCP DANIEL GARCIA</t>
+          <t>LOURDES PALACIOS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FISCALIZACIÓN A DESTIEMPO</t>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO D</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RESPONSABLE INGRESO SKU A DESTIEMPO.</t>
+          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -611,19 +605,20 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>COB_124837_0.jpeg</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>COBRO</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ID_20260602160039</t>
-        </is>
-      </c>
+          <t>ID_20260603101053</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -648,7 +643,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DEVOLUCION</t>
+          <t>RECEPCION</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -658,35 +653,40 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TIPO D</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="n">
+          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>COB_124837_0.jpeg</t>
+          <t>SIN_FOTO</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>COBRO</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ID_20260603101053</t>
+          <t>ID_20260603100142</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>INC_124933_0.png INC_124933_1.png</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+          <t>LATIN FRUITS C.A</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>37031</t>
+          <t>006886</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LOURDES PALACIOS</t>
+          <t xml:space="preserve">GERENTE LOURDES PALACIOS </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FISCALIZACIÓN A DESTIEMPO</t>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
+          <t>RESPONSABLE MONTO COPIA DE FACTURA Y LA MISMA SERA REEMPLAZADA</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -751,12 +751,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ID_20260603100142</t>
+          <t>ID_20260602170712</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>INC_124933_0.png INC_124933_1.png</t>
+          <t>INC_125257_0.png</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LATIN FRUITS C.A</t>
+          <t>MUSACEUM C.A</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>006886</t>
+          <t>36866</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -783,27 +783,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>DEVOLUCION</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">GERENTE LOURDES PALACIOS </t>
+          <t>PCP DANIEL  GARCIA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DOCUMENTACIÓN ERRÓNEA</t>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO A</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>RESPONSABLE MONTO COPIA DE FACTURA Y LA MISMA SERA REEMPLAZADA</t>
+          <t>RESPONSABLE NO COLOCO PESO DE TARA EN EL APLICATIVO</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -821,80 +821,10 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ID_20260602170712</t>
+          <t>ID_20260602155545</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
-        <is>
-          <t>INC_125257_0.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ACACIAS</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>MUSACEUM C.A</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>36866</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>DEVOLUCION</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>PCP DANIEL  GARCIA</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>TIPO A</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>RESPONSABLE NO COLOCO PESO DE TARA EN EL APLICATIVO</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>SIN_FOTO</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>NINGUNA</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>ID_20260602155545</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
         <is>
           <t>INC_130212_0.png INC_130212_1.png</t>
         </is>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>INC_124933_0.png INC_124933_1.png</t>
+          <t>INC_124933_0.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -552,7 +559,6 @@
           <t>ID_20260602085124</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -600,7 +606,7 @@
           <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -618,7 +624,6 @@
           <t>ID_20260603101053</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -628,17 +633,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+          <t>LATIN FRUITS C.A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>37031</t>
+          <t>006886</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -648,12 +653,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LOURDES PALACIOS</t>
+          <t xml:space="preserve">GERENTE LOURDES PALACIOS </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FISCALIZACIÓN A DESTIEMPO</t>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -663,7 +668,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
+          <t>RESPONSABLE MONTO COPIA DE FACTURA Y LA MISMA SERA REEMPLAZADA</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -681,12 +686,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ID_20260603100142</t>
+          <t>ID_20260602170712</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>INC_124933_0.png</t>
+          <t>INC_125257_0.png</t>
         </is>
       </c>
     </row>
@@ -698,12 +703,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LATIN FRUITS C.A</t>
+          <t>MUSACEUM C.A</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>006886</t>
+          <t>36866</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -713,27 +718,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>DEVOLUCION</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GERENTE LOURDES PALACIOS </t>
+          <t>PCP DANIEL  GARCIA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DOCUMENTACIÓN ERRÓNEA</t>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO A</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>RESPONSABLE MONTO COPIA DE FACTURA Y LA MISMA SERA REEMPLAZADA</t>
+          <t>RESPONSABLE NO COLOCO PESO DE TARA EN EL APLICATIVO</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -751,12 +756,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ID_20260602170712</t>
+          <t>ID_20260602155545</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>INC_125257_0.png</t>
+          <t>INC_130212_0.png INC_130212_1.png</t>
         </is>
       </c>
     </row>
@@ -768,42 +773,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MUSACEUM C.A</t>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>36866</t>
+          <t>37031</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DEVOLUCION</t>
+          <t>RECEPCION</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PCP DANIEL  GARCIA</t>
+          <t>LOURDES PALACIOS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TIPO A</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>RESPONSABLE NO COLOCO PESO DE TARA EN EL APLICATIVO</t>
+          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -821,12 +826,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ID_20260602155545</t>
+          <t>ID_20260603100142</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>INC_130212_0.png INC_130212_1.png</t>
+          <t>INC_124933_0.png INC_130401_0.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -559,6 +552,7 @@
           <t>ID_20260602085124</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -606,7 +600,7 @@
           <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
         </is>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -624,6 +618,7 @@
           <t>ID_20260603101053</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -689,11 +684,7 @@
           <t>ID_20260602170712</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>INC_125257_0.png</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -552,7 +559,6 @@
           <t>ID_20260602085124</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -600,7 +606,7 @@
           <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -618,7 +624,6 @@
           <t>ID_20260603101053</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -628,12 +633,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LATIN FRUITS C.A</t>
+          <t>MUSACEUM C.A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>006886</t>
+          <t>36866</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -643,27 +648,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>DEVOLUCION</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GERENTE LOURDES PALACIOS </t>
+          <t>PCP DANIEL  GARCIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DOCUMENTACIÓN ERRÓNEA</t>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO A</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>RESPONSABLE MONTO COPIA DE FACTURA Y LA MISMA SERA REEMPLAZADA</t>
+          <t>RESPONSABLE NO COLOCO PESO DE TARA EN EL APLICATIVO</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -681,10 +686,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ID_20260602170712</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>ID_20260602155545</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>INC_130212_0.png INC_130212_1.png</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -694,42 +703,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MUSACEUM C.A</t>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>36866</t>
+          <t>37031</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DEVOLUCION</t>
+          <t>RECEPCION</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PCP DANIEL  GARCIA</t>
+          <t>LOURDES PALACIOS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TIPO A</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>RESPONSABLE NO COLOCO PESO DE TARA EN EL APLICATIVO</t>
+          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -747,12 +756,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ID_20260602155545</t>
+          <t>ID_20260603100142</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>INC_130212_0.png INC_130212_1.png</t>
+          <t>INC_124933_0.png INC_130401_0.png</t>
         </is>
       </c>
     </row>
@@ -764,17 +773,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+          <t>LATIN FRUITS C.A</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37031</t>
+          <t>006886</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,12 +793,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LOURDES PALACIOS</t>
+          <t xml:space="preserve">GERENTE LOURDES PALACIOS </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FISCALIZACIÓN A DESTIEMPO</t>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -799,7 +808,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
+          <t>RESPONSABLE MONTO COPIA DE FACTURA Y LA MISMA SERA REEMPLAZADA</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -817,12 +826,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ID_20260603100142</t>
+          <t>ID_20260602170712</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>INC_124933_0.png INC_130401_0.png</t>
+          <t>INC_130507_0.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -559,6 +552,7 @@
           <t>ID_20260602085124</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -606,7 +600,7 @@
           <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
         </is>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -624,6 +618,7 @@
           <t>ID_20260603101053</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -691,7 +686,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>INC_130212_0.png INC_130212_1.png</t>
+          <t>INC_130212_1.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -552,7 +559,6 @@
           <t>ID_20260602085124</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -600,7 +606,7 @@
           <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -618,7 +624,6 @@
           <t>ID_20260603101053</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -628,42 +633,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MUSACEUM C.A</t>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>36866</t>
+          <t>37031</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DEVOLUCION</t>
+          <t>RECEPCION</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PCP DANIEL  GARCIA</t>
+          <t>LOURDES PALACIOS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TIPO A</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>RESPONSABLE NO COLOCO PESO DE TARA EN EL APLICATIVO</t>
+          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -681,12 +686,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ID_20260602155545</t>
+          <t>ID_20260603100142</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>INC_130212_1.png</t>
+          <t>INC_124933_0.png INC_130401_0.png</t>
         </is>
       </c>
     </row>
@@ -698,17 +703,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+          <t>LATIN FRUITS C.A</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>37031</t>
+          <t>006886</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -718,12 +723,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LOURDES PALACIOS</t>
+          <t xml:space="preserve">GERENTE LOURDES PALACIOS </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FISCALIZACIÓN A DESTIEMPO</t>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -733,7 +738,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
+          <t>RESPONSABLE MONTO COPIA DE FACTURA Y LA MISMA SERA REEMPLAZADA</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -751,12 +756,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ID_20260603100142</t>
+          <t>ID_20260602170712</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>INC_124933_0.png INC_130401_0.png</t>
+          <t>INC_130507_0.png</t>
         </is>
       </c>
     </row>
@@ -768,12 +773,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LATIN FRUITS C.A</t>
+          <t>MUSACEUM C.A</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>006886</t>
+          <t>36866</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -783,27 +788,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>DEVOLUCION</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">GERENTE LOURDES PALACIOS </t>
+          <t>PCP DANIEL  GARCIA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DOCUMENTACIÓN ERRÓNEA</t>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO A</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>RESPONSABLE MONTO COPIA DE FACTURA Y LA MISMA SERA REEMPLAZADA</t>
+          <t>RESPONSABLE NO COLOCO PESO DE TARA EN EL APLICATIVO</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -821,12 +826,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ID_20260602170712</t>
+          <t>ID_20260602155545</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>INC_130507_0.png</t>
+          <t>INC_130212_1.png INC_130959_0.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DEVOLUCION</t>
+          <t>RECEPCION</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -593,35 +593,40 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TIPO D</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="n">
+          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>COB_124837_0.jpeg</t>
+          <t>SIN_FOTO</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>COBRO</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ID_20260603101053</t>
+          <t>ID_20260603100142</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>INC_124933_0.png INC_130401_0.png</t>
         </is>
       </c>
     </row>
@@ -633,17 +638,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+          <t>LATIN FRUITS C.A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>37031</t>
+          <t>006886</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -653,12 +658,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LOURDES PALACIOS</t>
+          <t xml:space="preserve">GERENTE LOURDES PALACIOS </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FISCALIZACIÓN A DESTIEMPO</t>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -668,7 +673,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
+          <t>RESPONSABLE MONTO COPIA DE FACTURA Y LA MISMA SERA REEMPLAZADA</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -686,12 +691,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ID_20260603100142</t>
+          <t>ID_20260602170712</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>INC_124933_0.png INC_130401_0.png</t>
+          <t>INC_130507_0.png</t>
         </is>
       </c>
     </row>
@@ -703,12 +708,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LATIN FRUITS C.A</t>
+          <t>MUSACEUM C.A</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>006886</t>
+          <t>36866</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -718,27 +723,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>DEVOLUCION</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GERENTE LOURDES PALACIOS </t>
+          <t>PCP DANIEL  GARCIA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DOCUMENTACIÓN ERRÓNEA</t>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO A</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>RESPONSABLE MONTO COPIA DE FACTURA Y LA MISMA SERA REEMPLAZADA</t>
+          <t>RESPONSABLE NO COLOCO PESO DE TARA EN EL APLICATIVO</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -756,12 +761,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ID_20260602170712</t>
+          <t>ID_20260602155545</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>INC_130507_0.png</t>
+          <t>INC_130212_1.png INC_130959_0.png</t>
         </is>
       </c>
     </row>
@@ -773,17 +778,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MUSACEUM C.A</t>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>36866</t>
+          <t>37031</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -793,45 +798,40 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PCP DANIEL  GARCIA</t>
+          <t>LOURDES PALACIOS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TIPO A</t>
+          <t>TIPO D</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>RESPONSABLE NO COLOCO PESO DE TARA EN EL APLICATIVO</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
+          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>COB_124837_0.jpeg</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>COBRO</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ID_20260602155545</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>INC_130212_1.png INC_130959_0.png</t>
+          <t>ID_20260603101053</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0</v>
+        <v>7.62</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -503,17 +503,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I.T.F, C.A</t>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>138016</t>
+          <t>37031</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,22 +523,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DIANA  BENAVIDES</t>
+          <t>LOURDES PALACIOS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>TIPO A</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>PCP NO COLOCO EL RESPECTIVO NUM DE CEDULA EN EL DORSO FACTURA</t>
+          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -556,7 +556,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ID_20260602085124</t>
+          <t>ID_20260603100142</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>INC_124933_0.png INC_130401_0.png</t>
         </is>
       </c>
     </row>
@@ -568,17 +573,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+          <t>LATIN FRUITS C.A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37031</t>
+          <t>006886</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,12 +593,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LOURDES PALACIOS</t>
+          <t xml:space="preserve">GERENTE LOURDES PALACIOS </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FISCALIZACIÓN A DESTIEMPO</t>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -603,7 +608,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESPONSABLE FISCALIZO RUBROS Y CARGO SKU A DESTIEMPO </t>
+          <t>RESPONSABLE MONTO COPIA DE FACTURA Y LA MISMA SERA REEMPLAZADA</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -621,12 +626,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ID_20260603100142</t>
+          <t>ID_20260602170712</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>INC_124933_0.png INC_130401_0.png</t>
+          <t>INC_130507_0.png</t>
         </is>
       </c>
     </row>
@@ -638,12 +643,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LATIN FRUITS C.A</t>
+          <t>MUSACEUM C.A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>006886</t>
+          <t>36866</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -653,27 +658,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>DEVOLUCION</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GERENTE LOURDES PALACIOS </t>
+          <t>PCP DANIEL  GARCIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DOCUMENTACIÓN ERRÓNEA</t>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO A</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>RESPONSABLE MONTO COPIA DE FACTURA Y LA MISMA SERA REEMPLAZADA</t>
+          <t>RESPONSABLE NO COLOCO PESO DE TARA EN EL APLICATIVO</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -691,12 +696,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ID_20260602170712</t>
+          <t>ID_20260602155545</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>INC_130507_0.png</t>
+          <t>INC_130212_1.png INC_130959_0.png</t>
         </is>
       </c>
     </row>
@@ -708,17 +713,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MUSACEUM C.A</t>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>36866</t>
+          <t>37031</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -728,45 +733,40 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PCP DANIEL  GARCIA</t>
+          <t>LOURDES PALACIOS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TIPO A</t>
+          <t>TIPO D</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>RESPONSABLE NO COLOCO PESO DE TARA EN EL APLICATIVO</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
+          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>7.62</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>COB_124837_0.jpeg</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>COBRO</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ID_20260602155545</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>INC_130212_1.png INC_130959_0.png</t>
+          <t>ID_20260603101053</t>
         </is>
       </c>
     </row>
@@ -778,60 +778,65 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+          <t>I.T.F, C.A</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37031</t>
+          <t>138016</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DEVOLUCION</t>
+          <t>RECEPCION</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LOURDES PALACIOS</t>
+          <t>DIANA  BENAVIDES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TIPO D</t>
+          <t>TIPO A</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>7.62</v>
+          <t>PCP NO COLOCO EL RESPECTIVO NUM DE CEDULA EN EL DORSO FACTURA</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>COB_124837_0.jpeg</t>
+          <t>SIN_FOTO</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>COBRO</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ID_20260603101053</t>
+          <t>ID_20260602085124</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>INC_131324_0.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -751,7 +744,7 @@
           <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
         </is>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" t="n">
         <v>7.62</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -769,6 +762,7 @@
           <t>ID_20260603101053</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -834,11 +828,7 @@
           <t>ID_20260602085124</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>INC_131324_0.png</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -744,7 +751,7 @@
           <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="1" t="n">
         <v>7.62</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -762,7 +769,6 @@
           <t>ID_20260603101053</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -828,7 +834,11 @@
           <t>ID_20260602085124</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>INC_131859_0.jpeg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,6 +837,71 @@
       <c r="N6" t="inlineStr">
         <is>
           <t>INC_131859_0.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ACACIAS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EL TUNAL, C.A. </t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0030174</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>OTRAS.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AL INGRESAR CAJAS DE HUEVOS ESTUCHE DE 6 UNDS ,SE VISUALIZA UN ESTUCHE  AVERIADO .EL MISMO FUE CANCELADO POR EL PROVEEDOR </t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>COB_142606_0.jpeg</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ID_20260603142606</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,7 +744,7 @@
           <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
         </is>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" t="n">
         <v>7.62</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -769,6 +762,7 @@
           <t>ID_20260603101053</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -837,71 +831,6 @@
       <c r="N6" t="inlineStr">
         <is>
           <t>INC_131859_0.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ACACIAS</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EL TUNAL, C.A. </t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0030174</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RECEPCION</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>PROVEEDOR</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>OTRAS.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AL INGRESAR CAJAS DE HUEVOS ESTUCHE DE 6 UNDS ,SE VISUALIZA UN ESTUCHE  AVERIADO .EL MISMO FUE CANCELADO POR EL PROVEEDOR </t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>COB_142606_0.jpeg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>NINGUNA</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>ID_20260603142606</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -744,7 +751,7 @@
           <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="1" t="n">
         <v>7.62</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -762,7 +769,6 @@
           <t>ID_20260603101053</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,6 +837,76 @@
       <c r="N6" t="inlineStr">
         <is>
           <t>INC_131859_0.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ACACIAS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CENTRAL </t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>012112</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSLEN OCHOA </t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>RESPONSABLE INICIA FISCALIZACION Y LOS SKU LOS AGREGA A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ID_20260604110350</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>INC_110350_0.png INC_110350_1.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -713,60 +713,65 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+          <t>I.T.F, C.A</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>37031</t>
+          <t>138016</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DEVOLUCION</t>
+          <t>RECEPCION</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LOURDES PALACIOS</t>
+          <t>DIANA  BENAVIDES</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TIPO D</t>
+          <t>TIPO A</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
-        </is>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>7.62</v>
+          <t>PCP NO COLOCO EL RESPECTIVO NUM DE CEDULA EN EL DORSO FACTURA</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>COB_124837_0.jpeg</t>
+          <t>SIN_FOTO</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>COBRO</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ID_20260603101053</t>
+          <t>ID_20260602085124</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>INC_131859_0.jpeg</t>
         </is>
       </c>
     </row>
@@ -778,42 +783,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>I.T.F, C.A</t>
+          <t xml:space="preserve">CENTRAL </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>138016</t>
+          <t>012112</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>TRANSFERENCIA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DIANA  BENAVIDES</t>
+          <t xml:space="preserve">OSLEN OCHOA </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TIPO A</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PCP NO COLOCO EL RESPECTIVO NUM DE CEDULA EN EL DORSO FACTURA</t>
+          <t>RESPONSABLE INICIA FISCALIZACION Y LOS SKU LOS AGREGA A DESTIEMPO</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -831,12 +836,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ID_20260602085124</t>
+          <t>ID_20260604110350</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>INC_131859_0.jpeg</t>
+          <t>INC_110350_0.png INC_110350_1.png</t>
         </is>
       </c>
     </row>
@@ -848,65 +853,65 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CENTRAL </t>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>012112</t>
+          <t>37031</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TRANSFERENCIA</t>
+          <t>DEVOLUCION</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSLEN OCHOA </t>
+          <t>LOURDES PALACIOS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FISCALIZACIÓN A DESTIEMPO</t>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO D</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>RESPONSABLE INICIA FISCALIZACION Y LOS SKU LOS AGREGA A DESTIEMPO</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
+          <t>SE REALIZA DEVOLUCION DE 2 BANDEJAS DE CHAMPIÑON EN DOCUMENTO Y SE FISCALIZA SOLO 1 BANDEJA</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>7.62</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>COB_124837_0.jpeg</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>COBRO</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ID_20260604110350</t>
+          <t>ID_20260603101053</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>INC_110350_0.png INC_110350_1.png</t>
+          <t>INC_074755_0.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,6 +912,76 @@
       <c r="N7" t="inlineStr">
         <is>
           <t>INC_074755_0.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ACACIAS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DISPOAVES 95, C.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>01583</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>GERENTE LOURDES PALACIOS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FALTO COLOCAR EL SELLO DE LA SUCURSAL EN EL DOCUMENTO</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ID_20260605143215</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>INC_143215_0.jpeg INC_143215_1.jpeg</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/ACACIAS.xlsx
+++ b/cuadros/JUNIO/ACACIAS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -982,6 +982,76 @@
       <c r="N8" t="inlineStr">
         <is>
           <t>INC_143215_0.jpeg INC_143215_1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ACACIAS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>001226</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SUB GERENTE DIANA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CARGARON A DESTIEMPO LA HORA DE CONTEO DE LA FISCALIZACION, HORA REAL DEL INICIO DE FISCALIZACION: 17:47:47</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ID_20260606101011</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>INC_101011_0.png INC_101011_1.png</t>
         </is>
       </c>
     </row>
